--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,6 +1569,136 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121416509</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100360</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flisbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>615185</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6658253</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fuktstråk i svag sluttning.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>121416509</v>
       </c>
       <c r="B10" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>121416509</v>
       </c>
       <c r="B10" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>121416509</v>
       </c>
       <c r="B10" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>121416509</v>
       </c>
       <c r="B10" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774523</v>
+        <v>121774454</v>
       </c>
       <c r="B11" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,21 +1717,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         <v>615381</v>
       </c>
       <c r="R11" t="n">
-        <v>6658172</v>
+        <v>6658162</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774454</v>
+        <v>121774672</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615381</v>
+        <v>615374</v>
       </c>
       <c r="R12" t="n">
-        <v>6658162</v>
+        <v>6658235</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,12 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121774156</v>
+        <v>121777883</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>91168</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,48 +1946,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615286</v>
+        <v>615598</v>
       </c>
       <c r="R13" t="n">
-        <v>6658089</v>
+        <v>6658038</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2024,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121778024</v>
+        <v>121773975</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,37 +2058,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615513</v>
+        <v>615259</v>
       </c>
       <c r="R14" t="n">
-        <v>6657993</v>
+        <v>6657884</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2163,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121774210</v>
+        <v>121774168</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2208,7 +2198,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2227,13 +2217,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615315</v>
+        <v>615285</v>
       </c>
       <c r="R15" t="n">
-        <v>6658067</v>
+        <v>6658092</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2262,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121777883</v>
+        <v>121774523</v>
       </c>
       <c r="B16" t="n">
-        <v>91168</v>
+        <v>78352</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,41 +2301,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615598</v>
+        <v>615381</v>
       </c>
       <c r="R16" t="n">
-        <v>6658038</v>
+        <v>6658172</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2374,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2374,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774168</v>
+        <v>121777837</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,52 +2418,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615285</v>
+        <v>615605</v>
       </c>
       <c r="R17" t="n">
-        <v>6658092</v>
+        <v>6658036</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2500,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2491,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121774672</v>
+        <v>121778024</v>
       </c>
       <c r="B18" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,37 +2534,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615374</v>
+        <v>615513</v>
       </c>
       <c r="R18" t="n">
-        <v>6658235</v>
+        <v>6657993</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2612,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2766,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121773975</v>
+        <v>121774156</v>
       </c>
       <c r="B20" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2778,50 +2759,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615259</v>
+        <v>615286</v>
       </c>
       <c r="R20" t="n">
-        <v>6657884</v>
+        <v>6658089</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2850,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121777837</v>
+        <v>121774210</v>
       </c>
       <c r="B21" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,41 +2885,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615605</v>
+        <v>615315</v>
       </c>
       <c r="R21" t="n">
-        <v>6658036</v>
+        <v>6658067</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,7 +1701,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774454</v>
+        <v>121778024</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1737,17 +1737,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615381</v>
+        <v>615513</v>
       </c>
       <c r="R11" t="n">
-        <v>6658162</v>
+        <v>6657993</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,12 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774672</v>
+        <v>121774156</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,38 +1825,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615374</v>
+        <v>615286</v>
       </c>
       <c r="R12" t="n">
-        <v>6658235</v>
+        <v>6658089</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1893,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121777883</v>
+        <v>121774288</v>
       </c>
       <c r="B13" t="n">
-        <v>91168</v>
+        <v>56561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,41 +1951,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615598</v>
+        <v>615357</v>
       </c>
       <c r="R13" t="n">
-        <v>6658038</v>
+        <v>6658103</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121773975</v>
+        <v>121777837</v>
       </c>
       <c r="B14" t="n">
-        <v>57510</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,46 +2072,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615259</v>
+        <v>615605</v>
       </c>
       <c r="R14" t="n">
-        <v>6657884</v>
+        <v>6658036</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2289,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121774523</v>
+        <v>121773975</v>
       </c>
       <c r="B16" t="n">
-        <v>78352</v>
+        <v>57510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,37 +2310,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615381</v>
+        <v>615259</v>
       </c>
       <c r="R16" t="n">
-        <v>6658172</v>
+        <v>6657884</v>
       </c>
       <c r="S16" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,12 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121777837</v>
+        <v>121777883</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>91168</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,25 +2427,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615605</v>
+        <v>615598</v>
       </c>
       <c r="R17" t="n">
-        <v>6658036</v>
+        <v>6658038</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2481,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121778024</v>
+        <v>121774210</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,41 +2539,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615513</v>
+        <v>615315</v>
       </c>
       <c r="R18" t="n">
-        <v>6657993</v>
+        <v>6658067</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121774288</v>
+        <v>121774672</v>
       </c>
       <c r="B19" t="n">
-        <v>56561</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,42 +2669,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615357</v>
+        <v>615374</v>
       </c>
       <c r="R19" t="n">
-        <v>6658103</v>
+        <v>6658235</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2738,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121774156</v>
+        <v>121774454</v>
       </c>
       <c r="B20" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,52 +2777,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615286</v>
+        <v>615381</v>
       </c>
       <c r="R20" t="n">
-        <v>6658089</v>
+        <v>6658162</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2836,7 +2840,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2850,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774210</v>
+        <v>121774523</v>
       </c>
       <c r="B21" t="n">
-        <v>98113</v>
+        <v>78352</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,55 +2894,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615315</v>
+        <v>615381</v>
       </c>
       <c r="R21" t="n">
-        <v>6658067</v>
+        <v>6658172</v>
       </c>
       <c r="S21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2967,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121778024</v>
+        <v>121774156</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,41 +1713,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615513</v>
+        <v>615286</v>
       </c>
       <c r="R11" t="n">
-        <v>6657993</v>
+        <v>6658089</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774156</v>
+        <v>121774672</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,52 +1839,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615286</v>
+        <v>615374</v>
       </c>
       <c r="R12" t="n">
-        <v>6658089</v>
+        <v>6658235</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121774288</v>
+        <v>121774454</v>
       </c>
       <c r="B13" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,42 +1955,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615357</v>
+        <v>615381</v>
       </c>
       <c r="R13" t="n">
-        <v>6658103</v>
+        <v>6658162</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2024,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121777837</v>
+        <v>121777883</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>91168</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,25 +2068,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615605</v>
+        <v>615598</v>
       </c>
       <c r="R14" t="n">
-        <v>6658036</v>
+        <v>6658038</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121774168</v>
+        <v>121774210</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615285</v>
+        <v>615315</v>
       </c>
       <c r="R15" t="n">
-        <v>6658092</v>
+        <v>6658067</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121773975</v>
+        <v>121774523</v>
       </c>
       <c r="B16" t="n">
-        <v>57510</v>
+        <v>78352</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,46 +2310,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615259</v>
+        <v>615381</v>
       </c>
       <c r="R16" t="n">
-        <v>6657884</v>
+        <v>6658172</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2379,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121777883</v>
+        <v>121774168</v>
       </c>
       <c r="B17" t="n">
-        <v>91168</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,34 +2427,48 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615598</v>
+        <v>615285</v>
       </c>
       <c r="R17" t="n">
-        <v>6658038</v>
+        <v>6658092</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2490,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,10 +2537,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121774210</v>
+        <v>121778024</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,55 +2549,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615315</v>
+        <v>615513</v>
       </c>
       <c r="R18" t="n">
-        <v>6658067</v>
+        <v>6657993</v>
       </c>
       <c r="S18" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2616,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,7 +2649,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121774672</v>
+        <v>121777837</v>
       </c>
       <c r="B19" t="n">
         <v>90728</v>
@@ -2689,14 +2685,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615374</v>
+        <v>615605</v>
       </c>
       <c r="R19" t="n">
-        <v>6658235</v>
+        <v>6658036</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2728,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2738,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121774454</v>
+        <v>121774288</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2781,37 +2777,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615381</v>
+        <v>615357</v>
       </c>
       <c r="R20" t="n">
-        <v>6658162</v>
+        <v>6658103</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2840,7 +2841,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,12 +2851,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2878,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774523</v>
+        <v>121773975</v>
       </c>
       <c r="B21" t="n">
-        <v>78352</v>
+        <v>57510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,37 +2894,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615381</v>
+        <v>615259</v>
       </c>
       <c r="R21" t="n">
-        <v>6658172</v>
+        <v>6657884</v>
       </c>
       <c r="S21" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,12 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774156</v>
+        <v>121777883</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>91168</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,48 +1717,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615286</v>
+        <v>615598</v>
       </c>
       <c r="R11" t="n">
-        <v>6658089</v>
+        <v>6658038</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1790,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774672</v>
+        <v>121774210</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,41 +1825,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615374</v>
+        <v>615315</v>
       </c>
       <c r="R12" t="n">
-        <v>6658235</v>
+        <v>6658067</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121777883</v>
+        <v>121777837</v>
       </c>
       <c r="B14" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,25 +2068,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615598</v>
+        <v>615605</v>
       </c>
       <c r="R14" t="n">
-        <v>6658038</v>
+        <v>6658036</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121774210</v>
+        <v>121774672</v>
       </c>
       <c r="B15" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,55 +2180,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615315</v>
+        <v>615374</v>
       </c>
       <c r="R15" t="n">
-        <v>6658067</v>
+        <v>6658235</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121774523</v>
+        <v>121778024</v>
       </c>
       <c r="B16" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,37 +2296,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615381</v>
+        <v>615513</v>
       </c>
       <c r="R16" t="n">
-        <v>6658172</v>
+        <v>6657993</v>
       </c>
       <c r="S16" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,12 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774168</v>
+        <v>121774288</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>56561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,40 +2404,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,13 +2437,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615285</v>
+        <v>615357</v>
       </c>
       <c r="R17" t="n">
-        <v>6658092</v>
+        <v>6658103</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2500,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121778024</v>
+        <v>121774168</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2549,41 +2521,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615513</v>
+        <v>615285</v>
       </c>
       <c r="R18" t="n">
-        <v>6657993</v>
+        <v>6658092</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2612,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121777837</v>
+        <v>121773975</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>57510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,37 +2651,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615605</v>
+        <v>615259</v>
       </c>
       <c r="R19" t="n">
-        <v>6658036</v>
+        <v>6657884</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2724,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121774288</v>
+        <v>121774523</v>
       </c>
       <c r="B20" t="n">
-        <v>56561</v>
+        <v>78352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,42 +2772,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615357</v>
+        <v>615381</v>
       </c>
       <c r="R20" t="n">
-        <v>6658103</v>
+        <v>6658172</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2841,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2851,7 +2841,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2878,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121773975</v>
+        <v>121774156</v>
       </c>
       <c r="B21" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,50 +2885,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615259</v>
+        <v>615286</v>
       </c>
       <c r="R21" t="n">
-        <v>6657884</v>
+        <v>6658089</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121777883</v>
+        <v>121774288</v>
       </c>
       <c r="B11" t="n">
-        <v>91168</v>
+        <v>56561</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,41 +1713,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615598</v>
+        <v>615357</v>
       </c>
       <c r="R11" t="n">
-        <v>6658038</v>
+        <v>6658103</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774210</v>
+        <v>121777883</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>91168</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,51 +1834,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615315</v>
+        <v>615598</v>
       </c>
       <c r="R12" t="n">
-        <v>6658067</v>
+        <v>6658038</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121774454</v>
+        <v>121774156</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,38 +1942,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615381</v>
+        <v>615286</v>
       </c>
       <c r="R13" t="n">
-        <v>6658162</v>
+        <v>6658089</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2014,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,12 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121778024</v>
+        <v>121774168</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,41 +2292,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615513</v>
+        <v>615285</v>
       </c>
       <c r="R16" t="n">
-        <v>6657993</v>
+        <v>6658092</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774288</v>
+        <v>121774210</v>
       </c>
       <c r="B17" t="n">
-        <v>56561</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,31 +2418,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2437,13 +2460,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615357</v>
+        <v>615315</v>
       </c>
       <c r="R17" t="n">
-        <v>6658103</v>
+        <v>6658067</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2472,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121774168</v>
+        <v>121773975</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,55 +2544,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615285</v>
+        <v>615259</v>
       </c>
       <c r="R18" t="n">
-        <v>6658092</v>
+        <v>6657884</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121773975</v>
+        <v>121778024</v>
       </c>
       <c r="B19" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,46 +2669,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615259</v>
+        <v>615513</v>
       </c>
       <c r="R19" t="n">
-        <v>6657884</v>
+        <v>6657993</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2719,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2738,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121774523</v>
+        <v>121774454</v>
       </c>
       <c r="B20" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,21 +2781,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2799,10 +2808,10 @@
         <v>615381</v>
       </c>
       <c r="R20" t="n">
-        <v>6658172</v>
+        <v>6658162</v>
       </c>
       <c r="S20" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2831,7 +2840,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2850,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774156</v>
+        <v>121774523</v>
       </c>
       <c r="B21" t="n">
-        <v>98113</v>
+        <v>78352</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,55 +2894,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615286</v>
+        <v>615381</v>
       </c>
       <c r="R21" t="n">
-        <v>6658089</v>
+        <v>6658172</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2967,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774288</v>
+        <v>121774672</v>
       </c>
       <c r="B11" t="n">
-        <v>56561</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,42 +1717,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615357</v>
+        <v>615374</v>
       </c>
       <c r="R11" t="n">
-        <v>6658103</v>
+        <v>6658235</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121777883</v>
+        <v>121774210</v>
       </c>
       <c r="B12" t="n">
-        <v>91168</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,37 +1829,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615598</v>
+        <v>615315</v>
       </c>
       <c r="R12" t="n">
-        <v>6658038</v>
+        <v>6658067</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121774156</v>
+        <v>121774523</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>78352</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,55 +1951,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615286</v>
+        <v>615381</v>
       </c>
       <c r="R13" t="n">
-        <v>6658089</v>
+        <v>6658172</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2024,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121777837</v>
+        <v>121774288</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>56561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,37 +2072,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615605</v>
+        <v>615357</v>
       </c>
       <c r="R14" t="n">
-        <v>6658036</v>
+        <v>6658103</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121774672</v>
+        <v>121773975</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>57510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,37 +2189,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615374</v>
+        <v>615259</v>
       </c>
       <c r="R15" t="n">
-        <v>6658235</v>
+        <v>6657884</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121774168</v>
+        <v>121774454</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,52 +2306,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615285</v>
+        <v>615381</v>
       </c>
       <c r="R16" t="n">
-        <v>6658092</v>
+        <v>6658162</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2379,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,7 +2411,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774210</v>
+        <v>121774156</v>
       </c>
       <c r="B17" t="n">
         <v>98113</v>
@@ -2441,7 +2446,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2460,13 +2465,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615315</v>
+        <v>615286</v>
       </c>
       <c r="R17" t="n">
-        <v>6658067</v>
+        <v>6658089</v>
       </c>
       <c r="S17" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2537,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121773975</v>
+        <v>121777883</v>
       </c>
       <c r="B18" t="n">
-        <v>57510</v>
+        <v>91168</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,50 +2549,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615259</v>
+        <v>615598</v>
       </c>
       <c r="R18" t="n">
-        <v>6657884</v>
+        <v>6658038</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2616,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121778024</v>
+        <v>121777837</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2669,21 +2665,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2693,13 +2689,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615513</v>
+        <v>615605</v>
       </c>
       <c r="R19" t="n">
-        <v>6657993</v>
+        <v>6658036</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2728,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2738,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,7 +2761,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121774454</v>
+        <v>121778024</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2801,17 +2797,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615381</v>
+        <v>615513</v>
       </c>
       <c r="R20" t="n">
-        <v>6658162</v>
+        <v>6657993</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2840,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,12 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774523</v>
+        <v>121774168</v>
       </c>
       <c r="B21" t="n">
-        <v>78352</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,41 +2885,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615381</v>
+        <v>615285</v>
       </c>
       <c r="R21" t="n">
-        <v>6658172</v>
+        <v>6658092</v>
       </c>
       <c r="S21" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,12 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -2411,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774156</v>
+        <v>121777883</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>91168</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,48 +2427,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615286</v>
+        <v>615598</v>
       </c>
       <c r="R17" t="n">
-        <v>6658089</v>
+        <v>6658038</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2500,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121777883</v>
+        <v>121774156</v>
       </c>
       <c r="B18" t="n">
-        <v>91168</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,34 +2539,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615598</v>
+        <v>615286</v>
       </c>
       <c r="R18" t="n">
-        <v>6658038</v>
+        <v>6658089</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774672</v>
+        <v>121774288</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>56569</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,37 +1717,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615374</v>
+        <v>615357</v>
       </c>
       <c r="R11" t="n">
-        <v>6658235</v>
+        <v>6658103</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774210</v>
+        <v>121777837</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>90742</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,55 +1830,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615315</v>
+        <v>615605</v>
       </c>
       <c r="R12" t="n">
-        <v>6658067</v>
+        <v>6658036</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121774523</v>
+        <v>121777883</v>
       </c>
       <c r="B13" t="n">
-        <v>78352</v>
+        <v>91182</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,41 +1942,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615381</v>
+        <v>615598</v>
       </c>
       <c r="R13" t="n">
-        <v>6658172</v>
+        <v>6658038</v>
       </c>
       <c r="S13" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,12 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121774288</v>
+        <v>121774454</v>
       </c>
       <c r="B14" t="n">
-        <v>56561</v>
+        <v>78629</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,42 +2058,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615357</v>
+        <v>615381</v>
       </c>
       <c r="R14" t="n">
-        <v>6658103</v>
+        <v>6658162</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2127,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121773975</v>
+        <v>121774210</v>
       </c>
       <c r="B15" t="n">
-        <v>57510</v>
+        <v>98131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,50 +2171,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615259</v>
+        <v>615315</v>
       </c>
       <c r="R15" t="n">
-        <v>6657884</v>
+        <v>6658067</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2258,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121774454</v>
+        <v>121773975</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57518</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,37 +2301,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615381</v>
+        <v>615259</v>
       </c>
       <c r="R16" t="n">
-        <v>6658162</v>
+        <v>6657884</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,12 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121777883</v>
+        <v>121774156</v>
       </c>
       <c r="B17" t="n">
-        <v>91168</v>
+        <v>98131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,34 +2422,48 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615598</v>
+        <v>615286</v>
       </c>
       <c r="R17" t="n">
-        <v>6658038</v>
+        <v>6658089</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2486,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121774156</v>
+        <v>121774168</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,7 +2567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2577,10 +2586,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615286</v>
+        <v>615285</v>
       </c>
       <c r="R18" t="n">
-        <v>6658089</v>
+        <v>6658092</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2612,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121777837</v>
+        <v>121774672</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2685,14 +2694,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615605</v>
+        <v>615374</v>
       </c>
       <c r="R19" t="n">
-        <v>6658036</v>
+        <v>6658235</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2724,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2764,7 +2773,7 @@
         <v>121778024</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2873,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774168</v>
+        <v>121774523</v>
       </c>
       <c r="B21" t="n">
-        <v>98113</v>
+        <v>78365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,55 +2894,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615285</v>
+        <v>615381</v>
       </c>
       <c r="R21" t="n">
-        <v>6658092</v>
+        <v>6658172</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2967,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1818,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121777837</v>
+        <v>121774156</v>
       </c>
       <c r="B12" t="n">
-        <v>90742</v>
+        <v>98133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,38 +1830,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615605</v>
+        <v>615286</v>
       </c>
       <c r="R12" t="n">
-        <v>6658036</v>
+        <v>6658089</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1893,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121777883</v>
+        <v>121774454</v>
       </c>
       <c r="B13" t="n">
-        <v>91182</v>
+        <v>78631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,38 +1956,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615598</v>
+        <v>615381</v>
       </c>
       <c r="R13" t="n">
-        <v>6658038</v>
+        <v>6658162</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2005,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121774454</v>
+        <v>121774672</v>
       </c>
       <c r="B14" t="n">
-        <v>78629</v>
+        <v>90744</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,21 +2077,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615381</v>
+        <v>615374</v>
       </c>
       <c r="R14" t="n">
-        <v>6658162</v>
+        <v>6658235</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2117,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,12 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121774210</v>
+        <v>121777837</v>
       </c>
       <c r="B15" t="n">
-        <v>98131</v>
+        <v>90744</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,55 +2185,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615315</v>
+        <v>615605</v>
       </c>
       <c r="R15" t="n">
-        <v>6658067</v>
+        <v>6658036</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121773975</v>
+        <v>121777883</v>
       </c>
       <c r="B16" t="n">
-        <v>57518</v>
+        <v>91184</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,50 +2297,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615259</v>
+        <v>615598</v>
       </c>
       <c r="R16" t="n">
-        <v>6657884</v>
+        <v>6658038</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774156</v>
+        <v>121774523</v>
       </c>
       <c r="B17" t="n">
-        <v>98131</v>
+        <v>78367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,55 +2409,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615286</v>
+        <v>615381</v>
       </c>
       <c r="R17" t="n">
-        <v>6658089</v>
+        <v>6658172</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2482,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121774168</v>
+        <v>121778024</v>
       </c>
       <c r="B18" t="n">
-        <v>98131</v>
+        <v>78631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,55 +2526,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615285</v>
+        <v>615513</v>
       </c>
       <c r="R18" t="n">
-        <v>6658092</v>
+        <v>6657993</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2621,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121774672</v>
+        <v>121773975</v>
       </c>
       <c r="B19" t="n">
-        <v>90742</v>
+        <v>57518</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,37 +2642,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615374</v>
+        <v>615259</v>
       </c>
       <c r="R19" t="n">
-        <v>6658235</v>
+        <v>6657884</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2733,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2743,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121778024</v>
+        <v>121774210</v>
       </c>
       <c r="B20" t="n">
-        <v>78629</v>
+        <v>98133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,41 +2759,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615513</v>
+        <v>615315</v>
       </c>
       <c r="R20" t="n">
-        <v>6657993</v>
+        <v>6658067</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2845,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774523</v>
+        <v>121774168</v>
       </c>
       <c r="B21" t="n">
-        <v>78365</v>
+        <v>98133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,41 +2885,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615381</v>
+        <v>615285</v>
       </c>
       <c r="R21" t="n">
-        <v>6658172</v>
+        <v>6658092</v>
       </c>
       <c r="S21" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,12 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774288</v>
+        <v>121774523</v>
       </c>
       <c r="B11" t="n">
-        <v>56569</v>
+        <v>78368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,42 +1717,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615357</v>
+        <v>615381</v>
       </c>
       <c r="R11" t="n">
-        <v>6658103</v>
+        <v>6658172</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1786,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774156</v>
+        <v>121777837</v>
       </c>
       <c r="B12" t="n">
-        <v>98133</v>
+        <v>90745</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,52 +1830,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615286</v>
+        <v>615605</v>
       </c>
       <c r="R12" t="n">
-        <v>6658089</v>
+        <v>6658036</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1907,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121774454</v>
+        <v>121777883</v>
       </c>
       <c r="B13" t="n">
-        <v>78631</v>
+        <v>91185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,38 +1942,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615381</v>
+        <v>615598</v>
       </c>
       <c r="R13" t="n">
-        <v>6658162</v>
+        <v>6658038</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2019,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121774672</v>
+        <v>121773975</v>
       </c>
       <c r="B14" t="n">
-        <v>90744</v>
+        <v>57518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,37 +2058,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615374</v>
+        <v>615259</v>
       </c>
       <c r="R14" t="n">
-        <v>6658235</v>
+        <v>6657884</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121777837</v>
+        <v>121774156</v>
       </c>
       <c r="B15" t="n">
-        <v>90744</v>
+        <v>98140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,38 +2175,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615605</v>
+        <v>615286</v>
       </c>
       <c r="R15" t="n">
-        <v>6658036</v>
+        <v>6658089</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2248,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121777883</v>
+        <v>121778024</v>
       </c>
       <c r="B16" t="n">
-        <v>91184</v>
+        <v>78632</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2301,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,13 +2329,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615598</v>
+        <v>615513</v>
       </c>
       <c r="R16" t="n">
-        <v>6658038</v>
+        <v>6657993</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2360,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774523</v>
+        <v>121774210</v>
       </c>
       <c r="B17" t="n">
-        <v>78367</v>
+        <v>98140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,41 +2413,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615381</v>
+        <v>615315</v>
       </c>
       <c r="R17" t="n">
-        <v>6658172</v>
+        <v>6658067</v>
       </c>
       <c r="S17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2472,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,12 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121778024</v>
+        <v>121774168</v>
       </c>
       <c r="B18" t="n">
-        <v>78631</v>
+        <v>98140</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,41 +2539,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615513</v>
+        <v>615285</v>
       </c>
       <c r="R18" t="n">
-        <v>6657993</v>
+        <v>6658092</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2589,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121773975</v>
+        <v>121774672</v>
       </c>
       <c r="B19" t="n">
-        <v>57518</v>
+        <v>90745</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,46 +2669,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615259</v>
+        <v>615374</v>
       </c>
       <c r="R19" t="n">
-        <v>6657884</v>
+        <v>6658235</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2738,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121774210</v>
+        <v>121774454</v>
       </c>
       <c r="B20" t="n">
-        <v>98133</v>
+        <v>78632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,55 +2777,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615315</v>
+        <v>615381</v>
       </c>
       <c r="R20" t="n">
-        <v>6658067</v>
+        <v>6658162</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2836,7 +2840,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2850,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774168</v>
+        <v>121774288</v>
       </c>
       <c r="B21" t="n">
-        <v>98133</v>
+        <v>56569</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,40 +2894,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615285</v>
+        <v>615357</v>
       </c>
       <c r="R21" t="n">
-        <v>6658092</v>
+        <v>6658103</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -2289,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121778024</v>
+        <v>121774210</v>
       </c>
       <c r="B16" t="n">
-        <v>78632</v>
+        <v>98140</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,41 +2301,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615513</v>
+        <v>615315</v>
       </c>
       <c r="R16" t="n">
-        <v>6657993</v>
+        <v>6658067</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774210</v>
+        <v>121778024</v>
       </c>
       <c r="B17" t="n">
-        <v>98140</v>
+        <v>78632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,55 +2427,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615315</v>
+        <v>615513</v>
       </c>
       <c r="R17" t="n">
-        <v>6658067</v>
+        <v>6657993</v>
       </c>
       <c r="S17" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774523</v>
+        <v>121774156</v>
       </c>
       <c r="B11" t="n">
-        <v>78368</v>
+        <v>98149</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,41 +1713,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615381</v>
+        <v>615286</v>
       </c>
       <c r="R11" t="n">
-        <v>6658172</v>
+        <v>6658089</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,12 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På kolad rot av gammal låga</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121777837</v>
+        <v>121774672</v>
       </c>
       <c r="B12" t="n">
-        <v>90745</v>
+        <v>90754</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,14 +1863,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615605</v>
+        <v>615374</v>
       </c>
       <c r="R12" t="n">
-        <v>6658036</v>
+        <v>6658235</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1893,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121777883</v>
+        <v>121773975</v>
       </c>
       <c r="B13" t="n">
-        <v>91185</v>
+        <v>57522</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,41 +1951,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flismossen, Flismossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615598</v>
+        <v>615259</v>
       </c>
       <c r="R13" t="n">
-        <v>6658038</v>
+        <v>6657884</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2033,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121773975</v>
+        <v>121774523</v>
       </c>
       <c r="B14" t="n">
-        <v>57518</v>
+        <v>78375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,46 +2076,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flismossen, Flismossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615259</v>
+        <v>615381</v>
       </c>
       <c r="R14" t="n">
-        <v>6657884</v>
+        <v>6658172</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2145,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kolad rot av gammal låga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121774156</v>
+        <v>121774210</v>
       </c>
       <c r="B15" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,7 +2212,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2217,13 +2231,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615286</v>
+        <v>615315</v>
       </c>
       <c r="R15" t="n">
-        <v>6658089</v>
+        <v>6658067</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2252,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121774210</v>
+        <v>121777883</v>
       </c>
       <c r="B16" t="n">
-        <v>98140</v>
+        <v>91194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,51 +2319,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615315</v>
+        <v>615598</v>
       </c>
       <c r="R16" t="n">
-        <v>6658067</v>
+        <v>6658038</v>
       </c>
       <c r="S16" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121778024</v>
+        <v>121774288</v>
       </c>
       <c r="B17" t="n">
-        <v>78632</v>
+        <v>56573</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,37 +2431,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615513</v>
+        <v>615357</v>
       </c>
       <c r="R17" t="n">
-        <v>6657993</v>
+        <v>6658103</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2490,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121774168</v>
+        <v>121778024</v>
       </c>
       <c r="B18" t="n">
-        <v>98140</v>
+        <v>78639</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,55 +2544,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615285</v>
+        <v>615513</v>
       </c>
       <c r="R18" t="n">
-        <v>6658092</v>
+        <v>6657993</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2616,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121774672</v>
+        <v>121774168</v>
       </c>
       <c r="B19" t="n">
-        <v>90745</v>
+        <v>98149</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,38 +2656,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615374</v>
+        <v>615285</v>
       </c>
       <c r="R19" t="n">
-        <v>6658235</v>
+        <v>6658092</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2728,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2738,7 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121774454</v>
+        <v>121777837</v>
       </c>
       <c r="B20" t="n">
-        <v>78632</v>
+        <v>90754</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2781,34 +2786,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615381</v>
+        <v>615605</v>
       </c>
       <c r="R20" t="n">
-        <v>6658162</v>
+        <v>6658036</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2840,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,12 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774288</v>
+        <v>121774454</v>
       </c>
       <c r="B21" t="n">
-        <v>56569</v>
+        <v>78639</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,42 +2898,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615357</v>
+        <v>615381</v>
       </c>
       <c r="R21" t="n">
-        <v>6658103</v>
+        <v>6658162</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2967,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -2303,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121777883</v>
+        <v>121774288</v>
       </c>
       <c r="B16" t="n">
-        <v>91194</v>
+        <v>56573</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,41 +2315,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615598</v>
+        <v>615357</v>
       </c>
       <c r="R16" t="n">
-        <v>6658038</v>
+        <v>6658103</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121774288</v>
+        <v>121777883</v>
       </c>
       <c r="B17" t="n">
-        <v>56573</v>
+        <v>91194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,46 +2432,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615357</v>
+        <v>615598</v>
       </c>
       <c r="R17" t="n">
-        <v>6658103</v>
+        <v>6658038</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121777837</v>
+        <v>121774454</v>
       </c>
       <c r="B20" t="n">
-        <v>90754</v>
+        <v>78639</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,34 +2786,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttermossen, Slåttermossen, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615605</v>
+        <v>615381</v>
       </c>
       <c r="R20" t="n">
-        <v>6658036</v>
+        <v>6658162</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2855,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera bålar på lågt hängande grenar på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121774454</v>
+        <v>121777837</v>
       </c>
       <c r="B21" t="n">
-        <v>78639</v>
+        <v>90754</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,34 +2903,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Slåttermossen, Slåttermossen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615381</v>
+        <v>615605</v>
       </c>
       <c r="R21" t="n">
-        <v>6658162</v>
+        <v>6658036</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,12 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera bålar på lågt hängande grenar på gran.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -2881,11 +2881,11 @@
         <v>121773975</v>
       </c>
       <c r="B21" t="n">
-        <v>57527</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">

--- a/artfynd/A 55274-2024 artfynd.xlsx
+++ b/artfynd/A 55274-2024 artfynd.xlsx
@@ -2881,7 +2881,7 @@
         <v>121773975</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
